--- a/public/certificate/clone_craft.xlsx
+++ b/public/certificate/clone_craft.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -262,6 +262,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -279,14 +287,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -852,28 +852,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -997,7 +997,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1011,18 +1011,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1085,7 +1086,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1099,7 +1100,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1113,7 +1114,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1127,7 +1128,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1141,7 +1142,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1155,7 +1156,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1169,7 +1170,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1183,7 +1184,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1197,7 +1198,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1211,7 +1212,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1225,7 +1226,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1239,7 +1240,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1253,7 +1254,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1267,7 +1268,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1281,7 +1282,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1295,7 +1296,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1309,7 +1310,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1338,7 +1339,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Sheet1-style" pivot="0" count="2" xr9:uid="{93F0AD1B-1106-4FDB-897E-6465618E1544}">
+    <tableStyle name="Sheet1-style" pivot="0" count="2" xr9:uid="{91D80F51-9F53-4915-81D4-06053B5C2EA8}">
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
       <tableStyleElement type="secondRowStripe" dxfId="17"/>
     </tableStyle>
@@ -1616,21 +1617,21 @@
       <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="8"/>
+      <c r="I2" s="9"/>
       <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="9" t="s">
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="8">
         <v>609351912613</v>
       </c>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="13"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="14"/>
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="5">
@@ -1657,21 +1658,21 @@
       <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="10"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="11" t="s">
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="14"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="15"/>
     </row>
     <row r="4" customHeight="1" spans="1:17">
       <c r="A4" s="1">
@@ -1704,17 +1705,17 @@
       <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="9" t="s">
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="8">
         <v>609378856124</v>
       </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="13"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" customHeight="1" spans="1:17">
       <c r="A5" s="5">
@@ -1741,21 +1742,21 @@
       <c r="H5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="11" t="s">
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="13">
         <v>646220448048</v>
       </c>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="15">
+      <c r="P5" s="11"/>
+      <c r="Q5" s="16">
         <v>7988877075</v>
       </c>
     </row>
@@ -1784,21 +1785,21 @@
       <c r="H6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="9"/>
       <c r="J6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="9" t="s">
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="8">
         <v>609642857976</v>
       </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="16">
+      <c r="P6" s="9"/>
+      <c r="Q6" s="17">
         <v>6205639974</v>
       </c>
     </row>
@@ -1827,21 +1828,21 @@
       <c r="H7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="11"/>
       <c r="J7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="11" t="s">
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="13">
         <v>609706476798</v>
       </c>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="15">
+      <c r="P7" s="11"/>
+      <c r="Q7" s="16">
         <v>9643974952</v>
       </c>
     </row>
@@ -1870,21 +1871,21 @@
       <c r="H8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="8"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="9" t="s">
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="8">
         <v>646372843525</v>
       </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="16">
+      <c r="P8" s="9"/>
+      <c r="Q8" s="17">
         <v>6386011818</v>
       </c>
     </row>
@@ -1919,17 +1920,17 @@
       <c r="J9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="11" t="s">
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="13">
         <v>609747214233</v>
       </c>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="15">
+      <c r="P9" s="11"/>
+      <c r="Q9" s="16">
         <v>9266893243</v>
       </c>
     </row>
@@ -1958,21 +1959,21 @@
       <c r="H10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="9" t="s">
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="8">
         <v>646329468422</v>
       </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="16">
+      <c r="P10" s="9"/>
+      <c r="Q10" s="17">
         <v>7500261134</v>
       </c>
     </row>
@@ -2007,17 +2008,17 @@
       <c r="J11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="11" t="s">
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="13">
         <v>222406659265</v>
       </c>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="15">
+      <c r="P11" s="11"/>
+      <c r="Q11" s="16">
         <v>9984249543</v>
       </c>
     </row>
@@ -2025,7 +2026,7 @@
       <c r="A12" s="1">
         <v>46120.6709527315</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2037,7 +2038,7 @@
       <c r="E12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>9639014252</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -2046,21 +2047,21 @@
       <c r="H12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="8"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="9" t="s">
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="8">
         <v>609812862439</v>
       </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="16">
+      <c r="P12" s="9"/>
+      <c r="Q12" s="17">
         <v>9639014252</v>
       </c>
     </row>
@@ -2098,16 +2099,16 @@
       <c r="K13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="11" t="s">
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="13">
         <v>144043506040</v>
       </c>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="15">
+      <c r="P13" s="11"/>
+      <c r="Q13" s="16">
         <v>9569942630</v>
       </c>
     </row>
@@ -2115,7 +2116,7 @@
       <c r="A14" s="1">
         <v>46120.7746639005</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="7" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2145,16 +2146,16 @@
       <c r="K14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="9" t="s">
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="8">
         <v>609861303320</v>
       </c>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="16">
+      <c r="P14" s="9"/>
+      <c r="Q14" s="17">
         <v>8299042270</v>
       </c>
     </row>
@@ -2189,17 +2190,17 @@
       <c r="J15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="11" t="s">
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="13">
         <v>609856122540</v>
       </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="15">
+      <c r="P15" s="11"/>
+      <c r="Q15" s="16">
         <v>7011035560</v>
       </c>
     </row>
@@ -2219,6 +2220,8 @@
     <hyperlink ref="N13" r:id="rId13" display="https://drive.google.com/open?id=1KwzF4-XskFtA7tTa9YEuU_Hv8EUF0Cp-"/>
     <hyperlink ref="N14" r:id="rId14" display="https://drive.google.com/open?id=1rugc1sXH7nH6N_pGH37coDs6rNeO54fS"/>
     <hyperlink ref="N15" r:id="rId15" display="https://drive.google.com/open?id=1Tsjjq3kVsA6cssb_Xd8fPqRlOjRKWQ5w"/>
+    <hyperlink ref="B12" r:id="rId16" display="kashyapriya2510@gmail.com"/>
+    <hyperlink ref="B14" r:id="rId17" display="vivek.ursmemorial@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
